--- a/data/trans_orig/P16A_2_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146945</t>
+          <t>148634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193888</t>
+          <t>196515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207594</t>
+          <t>208882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297693</t>
+          <t>297983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385667</t>
+          <t>388951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>478667</t>
+          <t>478125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441553</t>
+          <t>438926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488496</t>
+          <t>486807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427637</t>
+          <t>427347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>517736</t>
+          <t>516448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882105</t>
+          <t>882647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>975105</t>
+          <t>971821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112118</t>
+          <t>96834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268582</t>
+          <t>266199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348324</t>
+          <t>350613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>400378</t>
+          <t>400667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>394523</t>
+          <t>387909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>664097</t>
+          <t>664808</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924282</t>
+          <t>926665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080746</t>
+          <t>1096030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558273</t>
+          <t>557984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610327</t>
+          <t>608038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1487419</t>
+          <t>1486708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1756993</t>
+          <t>1763607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136714</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186370</t>
+          <t>187691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>318961</t>
+          <t>317616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>679085</t>
+          <t>696846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>466543</t>
+          <t>465883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>973452</t>
+          <t>957125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518310</t>
+          <t>516989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567966</t>
+          <t>568752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254281</t>
+          <t>236520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>614405</t>
+          <t>615750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664594</t>
+          <t>680921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1171503</t>
+          <t>1172163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204852</t>
+          <t>205352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261603</t>
+          <t>262832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>330820</t>
+          <t>332695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>452957</t>
+          <t>455389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570831</t>
+          <t>570474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>694895</t>
+          <t>692350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>665228</t>
+          <t>663999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>721979</t>
+          <t>721479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641975</t>
+          <t>639543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>764112</t>
+          <t>762237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1326868</t>
+          <t>1329413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1450932</t>
+          <t>1451289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>594040</t>
+          <t>599658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>847131</t>
+          <t>852926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1367959</t>
+          <t>1371287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1946538</t>
+          <t>1936484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2059043</t>
+          <t>2068179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2757995</t>
+          <t>2703878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2612686</t>
+          <t>2606891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2865777</t>
+          <t>2860159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1765742</t>
+          <t>1775796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2344321</t>
+          <t>2340993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4414102</t>
+          <t>4468219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5113054</t>
+          <t>5103918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_2_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171183</t>
+          <t>187399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148634</t>
+          <t>161638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196515</t>
+          <t>212243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>269521</t>
+          <t>288764</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208882</t>
+          <t>269376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297983</t>
+          <t>309520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>440705</t>
+          <t>476163</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>388951</t>
+          <t>444856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>478125</t>
+          <t>510484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>464258</t>
+          <t>503311</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438926</t>
+          <t>478467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486807</t>
+          <t>529072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>455809</t>
+          <t>445416</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427347</t>
+          <t>424660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>516448</t>
+          <t>464804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>920067</t>
+          <t>948726</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882647</t>
+          <t>914405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>971821</t>
+          <t>980033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>220288</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96834</t>
+          <t>192102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266199</t>
+          <t>249540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>374375</t>
+          <t>414652</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>350613</t>
+          <t>388000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>400667</t>
+          <t>442138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>577783</t>
+          <t>634940</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387909</t>
+          <t>593568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>664808</t>
+          <t>674804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>989457</t>
+          <t>828629</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>926665</t>
+          <t>799377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1096030</t>
+          <t>856815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>584276</t>
+          <t>656822</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557984</t>
+          <t>629336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608038</t>
+          <t>683474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1573733</t>
+          <t>1485451</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1486708</t>
+          <t>1445587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1763607</t>
+          <t>1526823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>160632</t>
+          <t>178478</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135928</t>
+          <t>154383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187691</t>
+          <t>206246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>464539</t>
+          <t>293310</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>317616</t>
+          <t>268796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>696846</t>
+          <t>317696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>625171</t>
+          <t>471787</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>465883</t>
+          <t>435954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>957125</t>
+          <t>508491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>544048</t>
+          <t>624595</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516989</t>
+          <t>596827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568752</t>
+          <t>648690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>468827</t>
+          <t>518949</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236520</t>
+          <t>494563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615750</t>
+          <t>543463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1012875</t>
+          <t>1143545</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>680921</t>
+          <t>1106841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1172163</t>
+          <t>1179378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>231677</t>
+          <t>241870</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205352</t>
+          <t>217275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262832</t>
+          <t>270156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>413519</t>
+          <t>442915</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>332695</t>
+          <t>413991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455389</t>
+          <t>471451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>645196</t>
+          <t>684785</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570474</t>
+          <t>645620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>692350</t>
+          <t>723492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>695154</t>
+          <t>748192</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>663999</t>
+          <t>719906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>721479</t>
+          <t>772787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>681413</t>
+          <t>676126</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639543</t>
+          <t>647590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762237</t>
+          <t>705050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1376567</t>
+          <t>1424319</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1329413</t>
+          <t>1385612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451289</t>
+          <t>1463484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>599658</t>
+          <t>775545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>852926</t>
+          <t>887853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1371287</t>
+          <t>1390477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1936484</t>
+          <t>1492474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2068179</t>
+          <t>2189604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2703878</t>
+          <t>2347341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2692917</t>
+          <t>2704727</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2606891</t>
+          <t>2644909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2860159</t>
+          <t>2757217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2190326</t>
+          <t>2297314</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1775796</t>
+          <t>2244480</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2340993</t>
+          <t>2346477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4883243</t>
+          <t>5002041</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4468219</t>
+          <t>4922375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5103918</t>
+          <t>5080112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
